--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -11,6 +11,7 @@
     <sheet name="카드결제기준" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="주간조정" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="계좌목록" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="정기지출분류" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -686,22 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="G2:G20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택해 주세요." type="list">
@@ -1810,4 +1795,760 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>정기지출명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>성격</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(안내) 성격: 정기=매월 자동 추정 반영 / 변동=외상대 등 금액 변동(추정 제외) / 제외</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TOP출금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>급여·인건비(대외비)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>기업콜마비앤에이치</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>한화생</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>허용</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대표 가지급금</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>한화스마트</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>신한주노바렉스</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>우리카드결제대금</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>우리카드 결제</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>국고_주식회사</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>원천세·국세</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>신한고은미이룸파트</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>사회보험</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4대보험</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한진주식회사</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>국민주식회사 아이디</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼성건</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>퇴직예약출금</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>METLIFE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NH기업카드</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ABL생명</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>국민SA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>주카카오</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>신한대구달서구주식</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>국민비즈월렛_쁘띠앤</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>세이브더칠드런</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>기업특허법인 다옴</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>하나임정아</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>농협한혜선</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>아이임대규</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>기업주써치엠</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>국민주식회사 에이팜</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>아이서원회계법인 대</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>국민주식회사 오애드</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>국민GFA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>농협주레인보우</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>전자결제</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>하나흥덕IT밸리관리</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>하나남경 노무법인</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SKB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>아이로펌더봄엄요한</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>국민엠제이테크노파크</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>기업주식회사 채널코</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>아이현종찬</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KB카드출금</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>국민카드 결제</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>코웨이렌탈</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>국민서울보증보험</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>적십자후원</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>대한사회복지회</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>코웨이멤버쉽</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LGU</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LGUMM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1829,8 +1829,6 @@
           <t>(안내) 성격: 정기=매월 자동 추정 반영 / 변동=외상대 등 금액 변동(추정 제외) / 제외</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1855,7 +1853,11 @@
           <t>기업콜마비앤에이치</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>정기</t>
@@ -1919,7 +1921,11 @@
           <t>신한주노바렉스</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>정기</t>
@@ -1966,7 +1972,11 @@
           <t>신한고은미이룸파트</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>정기</t>
@@ -1996,7 +2006,11 @@
           <t>한진주식회사</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>운반비</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2009,7 +2023,11 @@
           <t>국민주식회사 아이디</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2039,7 +2057,11 @@
           <t>퇴직예약출금</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>퇴직급여</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2052,7 +2074,11 @@
           <t>METLIFE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2065,7 +2091,11 @@
           <t>NH기업카드</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>법인카드(농협)</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2095,7 +2125,11 @@
           <t>미래</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2108,7 +2142,11 @@
           <t>국민SA</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2121,7 +2159,11 @@
           <t>주카카오</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2134,7 +2176,11 @@
           <t>KB</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2147,7 +2193,11 @@
           <t>신한대구달서구주식</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2160,7 +2210,11 @@
           <t>국민비즈월렛_쁘띠앤</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2173,7 +2227,11 @@
           <t>세이브더칠드런</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>기부금</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2186,7 +2244,11 @@
           <t>기업특허법인 다옴</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2199,7 +2261,11 @@
           <t>하나임정아</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2212,7 +2278,11 @@
           <t>농협한혜선</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>임차료</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2225,7 +2295,11 @@
           <t>아이임대규</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>임차료</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2238,7 +2312,11 @@
           <t>기업주써치엠</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2251,7 +2329,11 @@
           <t>국민주식회사 에이팜</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2264,7 +2346,11 @@
           <t>아이서원회계법인 대</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2277,7 +2363,11 @@
           <t>국민주식회사 오애드</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2290,7 +2380,11 @@
           <t>국민GFA</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2303,7 +2397,11 @@
           <t>농협주레인보우</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2316,7 +2414,11 @@
           <t>전자결제</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2329,7 +2431,11 @@
           <t>하나흥덕IT밸리관리</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>관리비</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2342,7 +2448,11 @@
           <t>하나남경 노무법인</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2355,7 +2465,11 @@
           <t>SN</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2368,7 +2482,11 @@
           <t>SKB</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>통신비</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2381,7 +2499,11 @@
           <t>아이로펌더봄엄요한</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2394,7 +2516,11 @@
           <t>국민엠제이테크노파크</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>관리비</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2407,7 +2533,11 @@
           <t>기업주식회사 채널코</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2420,7 +2550,11 @@
           <t>아이현종찬</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>임차료</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2450,7 +2584,11 @@
           <t>KT</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>통신비</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2463,7 +2601,11 @@
           <t>코웨이렌탈</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2476,7 +2618,11 @@
           <t>국민서울보증보험</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2489,7 +2635,11 @@
           <t>적십자후원</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>기부금</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2502,7 +2652,11 @@
           <t>대한사회복지회</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>기부금</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2515,7 +2669,11 @@
           <t>코웨이멤버쉽</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2528,7 +2686,11 @@
           <t>LGU</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>통신비</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>정기</t>
@@ -2541,7 +2703,11 @@
           <t>LGUMM</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>통신비</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>정기</t>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,987 +738,273 @@
       <c r="A2" s="4" t="n">
         <v>46295</v>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n">
-        <v>65040941</v>
-      </c>
+      <c r="B2" s="5" t="n">
+        <v>10021867</v>
+      </c>
+      <c r="C2" s="5" t="n"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>정기지출 추정(자동 초안): TOP출금 신뢰도 하</t>
+          <t>관계사 외상대 입금 추정(주식회사에이팜, 말일)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n">
-        <v>44600001</v>
-      </c>
+        <v>46326</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>10021867</v>
+      </c>
+      <c r="C3" s="5" t="n"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>정기지출 추정(자동 초안): 기업콜마비앤에이치 신뢰도 중</t>
+          <t>관계사 외상대 입금 추정(주식회사에이팜, 말일)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n">
-        <v>42006200</v>
-      </c>
+        <v>46356</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>10021867</v>
+      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>정기지출 추정(자동 초안): 한화생 신뢰도 중</t>
+          <t>관계사 외상대 입금 추정(주식회사에이팜, 말일)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>46306</v>
-      </c>
+      <c r="A5" s="4" t="n"/>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n">
-        <v>39250000</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 허용 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>46299</v>
-      </c>
+      <c r="A6" s="4" t="n"/>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 한화스마트 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>46279</v>
-      </c>
+      <c r="A7" s="4" t="n"/>
       <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n">
-        <v>26655210</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 신한주노바렉스 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>46288</v>
-      </c>
+      <c r="A8" s="4" t="n"/>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n">
-        <v>26105540</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 우리카드결제대금 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>46305</v>
-      </c>
+      <c r="A9" s="4" t="n"/>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n">
-        <v>16964733</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국고_주식회사 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>46305</v>
-      </c>
+      <c r="A10" s="4" t="n"/>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n">
-        <v>16732980</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 신한고은미이룸파트 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>46305</v>
-      </c>
+      <c r="A11" s="4" t="n"/>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n">
-        <v>16413167</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 사회보험 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>46295</v>
-      </c>
+      <c r="A12" s="4" t="n"/>
       <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n">
-        <v>10790260</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 한진주식회사 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>46304</v>
-      </c>
+      <c r="A13" s="4" t="n"/>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n">
-        <v>9157500</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민주식회사 아이디 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>46302</v>
-      </c>
+      <c r="A14" s="4" t="n"/>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n">
-        <v>8898225</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 삼성건 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>46295</v>
-      </c>
+      <c r="A15" s="4" t="n"/>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n">
-        <v>8156420</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 퇴직예약출금 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>46288</v>
-      </c>
+      <c r="A16" s="4" t="n"/>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n">
-        <v>7641812</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): METLIFE 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>46288</v>
-      </c>
+      <c r="A17" s="4" t="n"/>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n">
-        <v>6066502</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): NH기업카드 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>46280</v>
-      </c>
+      <c r="A18" s="4" t="n"/>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n">
-        <v>5001750</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): ABL생명 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>46301</v>
-      </c>
+      <c r="A19" s="4" t="n"/>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n">
-        <v>4494000</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 미래 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>46304</v>
-      </c>
+      <c r="A20" s="4" t="n"/>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n">
-        <v>4427500</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민SA 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>46283</v>
-      </c>
+      <c r="A21" s="4" t="n"/>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n">
-        <v>3757143</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 주카카오 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>46296</v>
-      </c>
+      <c r="A22" s="4" t="n"/>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n">
-        <v>2952747</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): KB 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>46305</v>
-      </c>
+      <c r="A23" s="4" t="n"/>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n">
-        <v>2659287</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 신한대구달서구주식 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>46284</v>
-      </c>
+      <c r="A24" s="4" t="n"/>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n">
-        <v>2290345</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민비즈월렛_쁘띠앤 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>46289</v>
-      </c>
+      <c r="A25" s="4" t="n"/>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 세이브더칠드런 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>46279</v>
-      </c>
+      <c r="A26" s="4" t="n"/>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n">
-        <v>1899591</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 기업특허법인 다옴 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>46292</v>
-      </c>
+      <c r="A27" s="4" t="n"/>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 농협한혜선 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>46283</v>
-      </c>
+      <c r="A28" s="4" t="n"/>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 아이임대규 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>46285</v>
-      </c>
+      <c r="A29" s="4" t="n"/>
       <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n">
-        <v>1533488</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 기업주써치엠 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>46293</v>
-      </c>
+      <c r="A30" s="4" t="n"/>
       <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n">
-        <v>1369025</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민주식회사 에이팜 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>46294</v>
-      </c>
+      <c r="A31" s="4" t="n"/>
       <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n">
-        <v>1348600</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 아이서원회계법인 대 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>46294</v>
-      </c>
+      <c r="A32" s="4" t="n"/>
       <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n">
-        <v>1045000</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민주식회사 오애드 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>46304</v>
-      </c>
+      <c r="A33" s="4" t="n"/>
       <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n">
-        <v>907500</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민GFA 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>46306</v>
-      </c>
+      <c r="A34" s="4" t="n"/>
       <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n">
-        <v>839960</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 농협주레인보우 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>46279</v>
-      </c>
+      <c r="A35" s="4" t="n"/>
       <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 전자결제 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>46294</v>
-      </c>
+      <c r="A36" s="4" t="n"/>
       <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n">
-        <v>586192</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 하나흥덕IT밸리관리 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>46292</v>
-      </c>
+      <c r="A37" s="4" t="n"/>
       <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n">
-        <v>449429</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 하나남경 노무법인 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>46287</v>
-      </c>
+      <c r="A38" s="4" t="n"/>
       <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n">
-        <v>231733</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): SN 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>46286</v>
-      </c>
+      <c r="A39" s="4" t="n"/>
       <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n">
-        <v>223019</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): SKB 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>46306</v>
-      </c>
+      <c r="A40" s="4" t="n"/>
       <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n">
-        <v>220000</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 아이로펌더봄엄요한 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>46295</v>
-      </c>
+      <c r="A41" s="4" t="n"/>
       <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n">
-        <v>214586</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민엠제이테크노파크 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>46304</v>
-      </c>
+      <c r="A42" s="4" t="n"/>
       <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n">
-        <v>198000</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 기업주식회사 채널코 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>46288</v>
-      </c>
+      <c r="A43" s="4" t="n"/>
       <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n">
-        <v>173250</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 아이현종찬 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>46280</v>
-      </c>
+      <c r="A44" s="4" t="n"/>
       <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n">
-        <v>139091</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): KB카드출금 신뢰도 중</t>
-        </is>
-      </c>
+      <c r="C44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>46290</v>
-      </c>
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n">
-        <v>113633</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): KT 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>46280</v>
-      </c>
+      <c r="A46" s="4" t="n"/>
       <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n">
-        <v>113398</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 코웨이렌탈 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>46305</v>
-      </c>
+      <c r="A47" s="4" t="n"/>
       <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n">
-        <v>113382</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 국민서울보증보험 신뢰도 하</t>
-        </is>
-      </c>
+      <c r="C47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>46280</v>
-      </c>
+      <c r="A48" s="4" t="n"/>
       <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 적십자후원 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>46298</v>
-      </c>
+      <c r="A49" s="4" t="n"/>
       <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 대한사회복지회 신뢰도 상</t>
-        </is>
-      </c>
+      <c r="C49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>46280</v>
-      </c>
+      <c r="A50" s="4" t="n"/>
       <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n">
-        <v>46867</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): 코웨이멤버쉽 신뢰도 상</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n">
-        <v>33990</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): LGU 신뢰도 중</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n">
-        <v>11000</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>정기지출 추정(자동 초안): LGUMM 신뢰도 중</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>10021867</v>
-      </c>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>관계사 외상대 입금 추정(주식회사에이팜, 말일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>10021867</v>
-      </c>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>관계사 외상대 입금 추정(주식회사에이팜, 말일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>46356</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>10021867</v>
-      </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>관계사 외상대 입금 추정(주식회사에이팜, 말일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n"/>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n"/>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="n"/>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="n"/>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="n"/>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="n"/>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="n"/>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="5" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="n"/>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="n"/>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="5" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="n"/>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="5" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="n"/>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="n"/>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="5" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="5" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="5" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -12,6 +12,7 @@
     <sheet name="주간조정" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="계좌목록" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="정기지출분류" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="공휴일" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2003,4 +2004,122 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(안내) 해마다 설날·추석·임시공휴일 등을 여기에 추가하세요. 일자·요일이 결과물에서 붉은 글자로 표시됩니다.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>추석 연휴</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>추석</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>추석 연휴</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>개천절</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>개천절 대체공휴일</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>한글날</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46381</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>성탄절</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>신정</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,6 @@
           <t>(안내) 해마다 설날·추석·임시공휴일 등을 여기에 추가하세요. 일자·요일이 결과물에서 붉은 글자로 표시됩니다.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>정기</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>변동</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>변동</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>정기</t>
+          <t>제외</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,6 @@
           <t>(안내) 해마다 설날·추석·임시공휴일 등을 여기에 추가하세요. 일자·요일이 결과물에서 붉은 글자로 표시됩니다.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1996,6 +1996,74 @@
         </is>
       </c>
       <c r="C54" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>국민네이버 apha</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>변동</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>주식회사에이팜건강</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>자계자 이체</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>변동</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>국민네이버 에이팜건</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>광고비</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>변동</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>국민주에이팜건강</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>자계자 이체</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>정기</t>
         </is>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/에이팜건강_자금계획_기준파일.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2064,6 +2064,19 @@
         </is>
       </c>
       <c r="C58" t="inlineStr">
+        <is>
+          <t>정기</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>가스</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
         <is>
           <t>정기</t>
         </is>
